--- a/artfynd/A 59730-2024 artfynd.xlsx
+++ b/artfynd/A 59730-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137445950</v>
       </c>
       <c r="B2" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137445140</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137444565</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137445252</v>
       </c>
       <c r="B5" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137444944</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137445761</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137444795</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137444443</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137444128</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137444339</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>137446350</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137446415</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>137444938</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>137446325</v>
       </c>
       <c r="B15" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137446553</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
